--- a/config/currency-wars-generated/templates/CurrencyWars.xlsx
+++ b/config/currency-wars-generated/templates/CurrencyWars.xlsx
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6035" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6035" uniqueCount="305">
   <si>
     <t>@table</t>
   </si>
@@ -184,6 +184,9 @@
   </si>
   <si>
     <t>length=2..32767</t>
+  </si>
+  <si>
+    <t>length=0..32767</t>
   </si>
   <si>
     <t>#desc</t>
@@ -1730,24 +1733,24 @@
         <v>36</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:19" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -1802,7 +1805,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -1826,7 +1829,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="24" customHeight="1">
@@ -1873,13 +1876,13 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:17">
@@ -1926,13 +1929,13 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -2085,18 +2088,18 @@
         <v>36</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -2149,7 +2152,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -2173,7 +2176,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="24" customHeight="1">
@@ -2220,19 +2223,19 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -2279,19 +2282,19 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="S3" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -2456,24 +2459,24 @@
         <v>36</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:19" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -2529,7 +2532,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -2553,7 +2556,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="24" customHeight="1">
@@ -2600,16 +2603,16 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -2656,16 +2659,16 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -2824,21 +2827,21 @@
         <v>36</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -2892,7 +2895,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -2916,7 +2919,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="24" customHeight="1">
@@ -2963,16 +2966,16 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -3019,16 +3022,16 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -3187,21 +3190,21 @@
         <v>36</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -3254,7 +3257,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -3278,7 +3281,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="24" customHeight="1">
@@ -3325,19 +3328,19 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -3384,19 +3387,19 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="S3" s="5" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -3561,24 +3564,24 @@
         <v>36</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:19" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -3634,7 +3637,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -3658,7 +3661,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="24" customHeight="1">
@@ -3705,16 +3708,16 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -3761,16 +3764,16 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -3929,21 +3932,21 @@
         <v>36</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -3999,7 +4002,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -4023,7 +4026,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="24" customHeight="1">
@@ -4070,16 +4073,16 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -4126,16 +4129,16 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -4294,21 +4297,21 @@
         <v>36</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -4363,7 +4366,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -4387,7 +4390,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="24" customHeight="1">
@@ -4434,13 +4437,13 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:17">
@@ -4487,13 +4490,13 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -4646,18 +4649,18 @@
         <v>36</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -4709,7 +4712,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -4733,7 +4736,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="24" customHeight="1">
@@ -4780,16 +4783,16 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -4836,16 +4839,16 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -5004,21 +5007,21 @@
         <v>36</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -5073,7 +5076,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -5097,7 +5100,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="24" customHeight="1">
@@ -5144,16 +5147,16 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -5200,16 +5203,16 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -5368,21 +5371,21 @@
         <v>36</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -5435,7 +5438,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -5459,7 +5462,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="24" customHeight="1">
@@ -5506,13 +5509,13 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="R2" s="3" t="s">
         <v>26</v>
@@ -5562,13 +5565,13 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="R3" s="5" t="s">
         <v>26</v>
@@ -5730,21 +5733,21 @@
         <v>36</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -5798,7 +5801,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -5822,7 +5825,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="24" customHeight="1">
@@ -5869,16 +5872,16 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -5925,16 +5928,16 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -6093,21 +6096,21 @@
         <v>36</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -6160,7 +6163,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -6184,7 +6187,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="24" customHeight="1">
@@ -6231,16 +6234,16 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -6287,16 +6290,16 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -6455,21 +6458,21 @@
         <v>36</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -6522,7 +6525,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -6546,7 +6549,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="24" customHeight="1">
@@ -6593,16 +6596,16 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -6649,16 +6652,16 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -6817,21 +6820,21 @@
         <v>36</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -6884,7 +6887,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -6908,7 +6911,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="24" customHeight="1">
@@ -6955,13 +6958,13 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="3" spans="1:17">
@@ -7008,13 +7011,13 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -7167,18 +7170,18 @@
         <v>36</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -7233,7 +7236,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -7257,7 +7260,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="24" customHeight="1">
@@ -7304,16 +7307,16 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -7360,16 +7363,16 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -7528,21 +7531,21 @@
         <v>36</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -7594,7 +7597,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -7618,7 +7621,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="24" customHeight="1">
@@ -7665,19 +7668,19 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -7724,19 +7727,19 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="S3" s="5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -7901,24 +7904,24 @@
         <v>36</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:19" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -7973,7 +7976,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -7997,7 +8000,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="24" customHeight="1">
@@ -8044,19 +8047,19 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -8103,19 +8106,19 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="S3" s="5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -8280,24 +8283,24 @@
         <v>36</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:19" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -8351,7 +8354,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -8375,7 +8378,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="24" customHeight="1">
@@ -8422,16 +8425,16 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -8478,16 +8481,16 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -8646,21 +8649,21 @@
         <v>36</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -8712,7 +8715,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -8736,7 +8739,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="24" customHeight="1">
@@ -8783,16 +8786,16 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -8839,16 +8842,16 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -9007,21 +9010,21 @@
         <v>36</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -9074,7 +9077,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -9098,7 +9101,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="24" customHeight="1">
@@ -9145,19 +9148,19 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -9204,19 +9207,19 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="S3" s="5" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -9381,24 +9384,24 @@
         <v>36</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:19" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -9453,7 +9456,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -9477,7 +9480,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="24" customHeight="1">
@@ -9524,16 +9527,16 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -9580,16 +9583,16 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -9748,21 +9751,21 @@
         <v>36</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -9814,7 +9817,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -9838,7 +9841,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="24" customHeight="1">
@@ -9885,16 +9888,16 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -9941,16 +9944,16 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -10109,21 +10112,21 @@
         <v>36</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -10178,7 +10181,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -10202,7 +10205,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="24" customHeight="1">
@@ -10249,16 +10252,16 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -10305,16 +10308,16 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -10473,21 +10476,21 @@
         <v>36</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -10541,7 +10544,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -10565,7 +10568,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="24" customHeight="1">
@@ -10612,16 +10615,16 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -10668,16 +10671,16 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -10836,21 +10839,21 @@
         <v>36</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -10904,7 +10907,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -10928,7 +10931,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="24" customHeight="1">
@@ -10975,16 +10978,16 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -11031,16 +11034,16 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -11199,21 +11202,21 @@
         <v>36</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -11267,7 +11270,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -11291,7 +11294,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="24" customHeight="1">
@@ -11338,16 +11341,16 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -11394,16 +11397,16 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -11562,21 +11565,21 @@
         <v>36</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -11628,7 +11631,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -11652,7 +11655,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="24" customHeight="1">
@@ -11699,19 +11702,19 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -11758,19 +11761,19 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="S3" s="5" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -11935,24 +11938,24 @@
         <v>36</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:19" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -12009,7 +12012,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -12033,7 +12036,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="24" customHeight="1">
@@ -12080,16 +12083,16 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -12136,16 +12139,16 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -12304,21 +12307,21 @@
         <v>36</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -12371,7 +12374,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -12395,7 +12398,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="24" customHeight="1">
@@ -12442,16 +12445,16 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -12498,16 +12501,16 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -12666,21 +12669,21 @@
         <v>36</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -12733,7 +12736,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -12757,7 +12760,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="24" customHeight="1">
@@ -12804,16 +12807,16 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -12860,16 +12863,16 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -13028,21 +13031,21 @@
         <v>36</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -13096,7 +13099,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -13120,7 +13123,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="24" customHeight="1">
@@ -13167,22 +13170,22 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -13229,22 +13232,22 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="S3" s="5" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="T3" s="5" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -13415,27 +13418,27 @@
         <v>36</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:20" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -13490,7 +13493,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -13514,7 +13517,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="24" customHeight="1">
@@ -13561,13 +13564,13 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="P2" s="3" t="s">
         <v>24</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="R2" s="3" t="s">
         <v>25</v>
@@ -13617,13 +13620,13 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="P3" s="5" t="s">
         <v>24</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="R3" s="5" t="s">
         <v>25</v>
@@ -13785,21 +13788,21 @@
         <v>36</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -13851,7 +13854,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -13875,7 +13878,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="24" customHeight="1">
@@ -13922,19 +13925,19 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -13981,19 +13984,19 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="S3" s="5" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -14158,24 +14161,24 @@
         <v>36</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:19" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -14228,7 +14231,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -14252,7 +14255,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="24" customHeight="1">
@@ -14299,13 +14302,13 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="3" spans="1:17">
@@ -14352,13 +14355,13 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -14511,18 +14514,18 @@
         <v>36</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -14573,7 +14576,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -14597,7 +14600,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="24" customHeight="1">
@@ -14644,10 +14647,10 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -14694,10 +14697,10 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -14844,15 +14847,15 @@
         <v>36</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -14902,7 +14905,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -14926,7 +14929,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="24" customHeight="1">
@@ -14973,16 +14976,16 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -15029,16 +15032,16 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -15197,21 +15200,21 @@
         <v>36</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -15263,7 +15266,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -15287,7 +15290,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="24" customHeight="1">
@@ -15337,10 +15340,10 @@
         <v>24</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="3" spans="1:17">
@@ -15390,10 +15393,10 @@
         <v>24</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -15546,18 +15549,18 @@
         <v>36</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -15608,7 +15611,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -15632,7 +15635,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="24" customHeight="1">
@@ -15679,13 +15682,13 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="3" spans="1:17">
@@ -15732,13 +15735,13 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -15891,18 +15894,18 @@
         <v>36</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -15954,7 +15957,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -15978,7 +15981,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="24" customHeight="1">
@@ -16025,10 +16028,10 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -16075,10 +16078,10 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -16225,15 +16228,15 @@
         <v>36</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -16283,7 +16286,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -16307,7 +16310,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="24" customHeight="1">
@@ -16354,16 +16357,16 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -16410,16 +16413,16 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -16578,21 +16581,21 @@
         <v>36</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -16644,7 +16647,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -16668,7 +16671,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="24" customHeight="1">
@@ -16715,19 +16718,19 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -16774,19 +16777,19 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="S3" s="5" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -16951,24 +16954,24 @@
         <v>36</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:19" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -17021,7 +17024,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -17045,7 +17048,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="24" customHeight="1">
@@ -17092,10 +17095,10 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -17142,10 +17145,10 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -17292,15 +17295,15 @@
         <v>36</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -17353,7 +17356,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -17377,7 +17380,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="24" customHeight="1">
@@ -17424,13 +17427,13 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:17">
@@ -17477,13 +17480,13 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -17636,18 +17639,18 @@
         <v>36</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -17698,7 +17701,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -17722,7 +17725,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="24" customHeight="1">
@@ -17769,19 +17772,19 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -17828,19 +17831,19 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="S3" s="5" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -18005,24 +18008,24 @@
         <v>36</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:19" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -18075,7 +18078,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -18099,7 +18102,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="24" customHeight="1">
@@ -18146,16 +18149,16 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -18202,16 +18205,16 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -18370,21 +18373,21 @@
         <v>36</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -18436,7 +18439,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -18460,7 +18463,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="24" customHeight="1">
@@ -18507,10 +18510,10 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -18557,10 +18560,10 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -18707,15 +18710,15 @@
         <v>36</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -18765,7 +18768,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -18789,7 +18792,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="24" customHeight="1">
@@ -18836,10 +18839,10 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -18886,10 +18889,10 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -19036,15 +19039,15 @@
         <v>36</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -19097,7 +19100,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -19121,7 +19124,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="24" customHeight="1">
@@ -19168,22 +19171,22 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -19230,22 +19233,22 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="S3" s="5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="T3" s="5" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -19416,27 +19419,27 @@
         <v>36</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:20" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -19492,7 +19495,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -19516,7 +19519,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="24" customHeight="1">
@@ -19563,16 +19566,16 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -19619,16 +19622,16 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -19787,21 +19790,21 @@
         <v>36</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -19856,7 +19859,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -19880,7 +19883,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="24" customHeight="1">
@@ -19927,19 +19930,19 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -19986,19 +19989,19 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="S3" s="5" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -20163,24 +20166,24 @@
         <v>36</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:19" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -20233,7 +20236,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -20257,7 +20260,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="24" customHeight="1">
@@ -20304,19 +20307,19 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -20363,19 +20366,19 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="S3" s="5" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -20540,24 +20543,24 @@
         <v>36</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:19" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -20612,7 +20615,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -20636,7 +20639,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="24" customHeight="1">
@@ -20683,16 +20686,16 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -20739,16 +20742,16 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -20907,21 +20910,21 @@
         <v>36</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -20975,7 +20978,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -20999,7 +21002,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="24" customHeight="1">
@@ -21046,13 +21049,13 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="3" spans="1:17">
@@ -21099,13 +21102,13 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -21258,18 +21261,18 @@
         <v>36</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -21321,7 +21324,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -21345,7 +21348,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="24" customHeight="1">
@@ -21392,13 +21395,13 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:17">
@@ -21445,13 +21448,13 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -21604,18 +21607,18 @@
         <v>36</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -21668,7 +21671,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -21692,7 +21695,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="24" customHeight="1">
@@ -21739,16 +21742,16 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -21795,16 +21798,16 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -21963,21 +21966,21 @@
         <v>36</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -22031,7 +22034,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -22055,7 +22058,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="24" customHeight="1">
@@ -22102,16 +22105,16 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -22158,16 +22161,16 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -22326,21 +22329,21 @@
         <v>36</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -22394,7 +22397,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -22418,7 +22421,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="24" customHeight="1">
@@ -22465,13 +22468,13 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:17">
@@ -22518,13 +22521,13 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -22677,18 +22680,18 @@
         <v>36</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -22740,7 +22743,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -22764,7 +22767,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="24" customHeight="1">
@@ -22811,13 +22814,13 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:17">
@@ -22864,13 +22867,13 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -23023,18 +23026,18 @@
         <v>36</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>

--- a/config/currency-wars-generated/templates/CurrencyWars.xlsx
+++ b/config/currency-wars-generated/templates/CurrencyWars.xlsx
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6035" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6085" uniqueCount="313">
   <si>
     <t>@table</t>
   </si>
@@ -327,7 +327,7 @@
     <t>CurrencyWarsNodes</t>
   </si>
   <si>
-    <t>fcc06569aa366c25</t>
+    <t>f02b0ac0cd2b5082</t>
   </si>
   <si>
     <t>layer_id</t>
@@ -342,6 +342,27 @@
     <t>room_pool_id</t>
   </si>
   <si>
+    <t>node_template_id</t>
+  </si>
+  <si>
+    <t>stage_id</t>
+  </si>
+  <si>
+    <t>node_type</t>
+  </si>
+  <si>
+    <t>parameter_ids</t>
+  </si>
+  <si>
+    <t>penalty_bonus_rule_id</t>
+  </si>
+  <si>
+    <t>basic_gold_reward</t>
+  </si>
+  <si>
+    <t>next_node_id</t>
+  </si>
+  <si>
     <t>CurrencyWarsDomainCompositions</t>
   </si>
   <si>
@@ -447,7 +468,7 @@
     <t>CurrencyWarsRosterAvatars</t>
   </si>
   <si>
-    <t>102876bc4cbb195f</t>
+    <t>77a3f7bb812b702a</t>
   </si>
   <si>
     <t>avatar_id</t>
@@ -456,12 +477,18 @@
     <t>cost</t>
   </si>
   <si>
+    <t>rarity</t>
+  </si>
+  <si>
     <t>role_id</t>
   </si>
   <si>
     <t>build_mapping_id</t>
   </si>
   <si>
+    <t>position_kind</t>
+  </si>
+  <si>
     <t>CurrencyWarsEconomyRules</t>
   </si>
   <si>
@@ -516,7 +543,7 @@
     <t>CurrencyWarsTeamSizeStates</t>
   </si>
   <si>
-    <t>83b2449ce83507fc</t>
+    <t>1b663b531aeb7279</t>
   </si>
   <si>
     <t>level</t>
@@ -528,6 +555,9 @@
     <t>bench_cap</t>
   </si>
   <si>
+    <t>next_level_experience</t>
+  </si>
+  <si>
     <t>CurrencyWarsRoleMappings</t>
   </si>
   <si>
@@ -544,9 +574,6 @@
   </si>
   <si>
     <t>97aa01b869b05be9</t>
-  </si>
-  <si>
-    <t>position_kind</t>
   </si>
   <si>
     <t>field_index</t>
@@ -2129,7 +2156,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S7"/>
+  <dimension ref="A1:Z7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -2143,10 +2170,13 @@
     <col min="14" max="14" width="12.7109375" style="5" customWidth="1"/>
     <col min="15" max="17" width="16.7109375" style="5" customWidth="1"/>
     <col min="18" max="18" width="21.7109375" style="5" customWidth="1"/>
-    <col min="19" max="19" width="16.7109375" style="5" customWidth="1"/>
+    <col min="19" max="23" width="16.7109375" style="5" customWidth="1"/>
+    <col min="24" max="24" width="21.7109375" style="5" customWidth="1"/>
+    <col min="25" max="25" width="17.7109375" style="5" customWidth="1"/>
+    <col min="26" max="26" width="16.7109375" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:26">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2178,7 +2208,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="24" customHeight="1">
+    <row r="2" spans="1:26" ht="24" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>10</v>
       </c>
@@ -2236,8 +2266,29 @@
       <c r="S2" s="3" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="3" spans="1:19">
+      <c r="T2" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="U2" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="V2" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="W2" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="X2" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="Y2" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="Z2" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26">
       <c r="A3" s="4" t="s">
         <v>28</v>
       </c>
@@ -2295,8 +2346,29 @@
       <c r="S3" s="5" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="4" spans="1:19">
+      <c r="T3" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="U3" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="V3" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="W3" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="X3" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="Y3" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="Z3" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26">
       <c r="A4" s="4" t="s">
         <v>29</v>
       </c>
@@ -2354,8 +2426,29 @@
       <c r="S4" s="5" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="5" spans="1:19">
+      <c r="T4" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="U4" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="V4" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="W4" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="X4" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y4" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z4" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26">
       <c r="A5" s="4" t="s">
         <v>33</v>
       </c>
@@ -2413,8 +2506,29 @@
       <c r="S5" s="5" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="6" spans="1:19">
+      <c r="T5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="U5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="V5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="W5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="X5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z5" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26">
       <c r="A6" s="4" t="s">
         <v>34</v>
       </c>
@@ -2472,8 +2586,29 @@
       <c r="S6" s="5" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="7" spans="1:19" ht="42" customHeight="1">
+      <c r="T6" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="U6" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="V6" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="W6" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="X6" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y6" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z6" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
         <v>37</v>
       </c>
@@ -2495,6 +2630,13 @@
       <c r="Q7" s="6"/>
       <c r="R7" s="6"/>
       <c r="S7" s="6"/>
+      <c r="T7" s="6"/>
+      <c r="U7" s="6"/>
+      <c r="V7" s="6"/>
+      <c r="W7" s="6"/>
+      <c r="X7" s="6"/>
+      <c r="Y7" s="6"/>
+      <c r="Z7" s="6"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -2531,7 +2673,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -2555,7 +2697,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="24" customHeight="1">
@@ -2602,16 +2744,16 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="Q2" s="3" t="s">
         <v>60</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -2658,16 +2800,16 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="Q3" s="5" t="s">
         <v>60</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -2895,7 +3037,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -2919,7 +3061,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="24" customHeight="1">
@@ -2966,16 +3108,16 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -3022,16 +3164,16 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -3257,7 +3399,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -3281,7 +3423,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="24" customHeight="1">
@@ -3328,19 +3470,19 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -3387,19 +3529,19 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="S3" s="5" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -3635,7 +3777,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -3659,7 +3801,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="24" customHeight="1">
@@ -3706,16 +3848,16 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -3762,16 +3904,16 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -4000,7 +4142,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -4024,7 +4166,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="24" customHeight="1">
@@ -4071,16 +4213,16 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -4127,16 +4269,16 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -4364,7 +4506,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -4388,7 +4530,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="24" customHeight="1">
@@ -4435,10 +4577,10 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="Q2" s="3" t="s">
         <v>56</v>
@@ -4488,10 +4630,10 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="Q3" s="5" t="s">
         <v>56</v>
@@ -4690,7 +4832,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R7"/>
+  <dimension ref="A1:T7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -4702,15 +4844,15 @@
     <col min="11" max="11" width="14.7109375" style="5" customWidth="1"/>
     <col min="12" max="13" width="16.7109375" style="5" customWidth="1"/>
     <col min="14" max="14" width="12.7109375" style="5" customWidth="1"/>
-    <col min="15" max="18" width="16.7109375" style="5" customWidth="1"/>
+    <col min="15" max="20" width="16.7109375" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:20">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -4734,10 +4876,10 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" ht="24" customHeight="1">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" ht="24" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>10</v>
       </c>
@@ -4781,19 +4923,25 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18">
+        <v>135</v>
+      </c>
+      <c r="S2" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20">
       <c r="A3" s="4" t="s">
         <v>28</v>
       </c>
@@ -4837,19 +4985,25 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18">
+        <v>135</v>
+      </c>
+      <c r="S3" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="T3" s="5" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20">
       <c r="A4" s="4" t="s">
         <v>29</v>
       </c>
@@ -4904,8 +5058,14 @@
       <c r="R4" s="5" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="5" spans="1:18">
+      <c r="S4" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="T4" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20">
       <c r="A5" s="4" t="s">
         <v>33</v>
       </c>
@@ -4960,8 +5120,14 @@
       <c r="R5" s="5" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="6" spans="1:18">
+      <c r="S5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="T5" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20">
       <c r="A6" s="4" t="s">
         <v>34</v>
       </c>
@@ -5016,8 +5182,14 @@
       <c r="R6" s="5" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="7" spans="1:18" ht="42" customHeight="1">
+      <c r="S6" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="T6" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
         <v>37</v>
       </c>
@@ -5038,6 +5210,8 @@
       <c r="P7" s="6"/>
       <c r="Q7" s="6"/>
       <c r="R7" s="6"/>
+      <c r="S7" s="6"/>
+      <c r="T7" s="6"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -5072,7 +5246,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -5096,7 +5270,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="24" customHeight="1">
@@ -5143,16 +5317,16 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -5199,16 +5373,16 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -5798,7 +5972,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -5822,7 +5996,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="24" customHeight="1">
@@ -5869,16 +6043,16 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -5925,16 +6099,16 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -6161,7 +6335,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -6185,7 +6359,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="24" customHeight="1">
@@ -6232,16 +6406,16 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -6288,16 +6462,16 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -6503,7 +6677,7 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R7"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -6515,15 +6689,17 @@
     <col min="11" max="11" width="14.7109375" style="5" customWidth="1"/>
     <col min="12" max="13" width="16.7109375" style="5" customWidth="1"/>
     <col min="14" max="14" width="12.7109375" style="5" customWidth="1"/>
-    <col min="15" max="18" width="16.7109375" style="5" customWidth="1"/>
+    <col min="15" max="17" width="16.7109375" style="5" customWidth="1"/>
+    <col min="18" max="18" width="21.7109375" style="5" customWidth="1"/>
+    <col min="19" max="19" width="16.7109375" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:19">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -6547,10 +6723,10 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" ht="24" customHeight="1">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" ht="24" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>10</v>
       </c>
@@ -6594,19 +6770,22 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="R2" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="S2" s="3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="3" spans="1:18">
+    <row r="3" spans="1:19">
       <c r="A3" s="4" t="s">
         <v>28</v>
       </c>
@@ -6650,19 +6829,22 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="R3" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="S3" s="5" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:18">
+    <row r="4" spans="1:19">
       <c r="A4" s="4" t="s">
         <v>29</v>
       </c>
@@ -6717,8 +6899,11 @@
       <c r="R4" s="5" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="5" spans="1:18">
+      <c r="S4" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19">
       <c r="A5" s="4" t="s">
         <v>33</v>
       </c>
@@ -6773,8 +6958,11 @@
       <c r="R5" s="5" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="6" spans="1:18">
+      <c r="S5" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19">
       <c r="A6" s="4" t="s">
         <v>34</v>
       </c>
@@ -6829,8 +7017,11 @@
       <c r="R6" s="5" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="7" spans="1:18" ht="42" customHeight="1">
+      <c r="S6" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
         <v>37</v>
       </c>
@@ -6851,6 +7042,7 @@
       <c r="P7" s="6"/>
       <c r="Q7" s="6"/>
       <c r="R7" s="6"/>
+      <c r="S7" s="6"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -6885,7 +7077,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -6909,7 +7101,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="24" customHeight="1">
@@ -6956,13 +7148,13 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
     </row>
     <row r="3" spans="1:17">
@@ -7009,13 +7201,13 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -7232,7 +7424,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -7256,7 +7448,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="24" customHeight="1">
@@ -7303,16 +7495,16 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -7359,16 +7551,16 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -7594,7 +7786,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -7618,7 +7810,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="24" customHeight="1">
@@ -7665,19 +7857,19 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -7724,19 +7916,19 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="S3" s="5" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -7974,7 +8166,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -7998,7 +8190,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="24" customHeight="1">
@@ -8045,19 +8237,19 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="Q2" s="3" t="s">
         <v>55</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -8104,19 +8296,19 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="Q3" s="5" t="s">
         <v>55</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="S3" s="5" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -8352,7 +8544,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -8376,7 +8568,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="24" customHeight="1">
@@ -8423,16 +8615,16 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -8479,16 +8671,16 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -8714,7 +8906,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -8738,7 +8930,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="24" customHeight="1">
@@ -8785,16 +8977,16 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -8841,16 +9033,16 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -9076,7 +9268,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -9100,7 +9292,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="24" customHeight="1">
@@ -9147,19 +9339,19 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -9206,19 +9398,19 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="S3" s="5" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -9816,7 +10008,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -9840,7 +10032,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="24" customHeight="1">
@@ -9887,16 +10079,16 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -9943,16 +10135,16 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -10178,7 +10370,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -10202,7 +10394,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="24" customHeight="1">
@@ -10249,16 +10441,16 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -10305,16 +10497,16 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -10540,7 +10732,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -10564,7 +10756,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="24" customHeight="1">
@@ -10611,16 +10803,16 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -10667,16 +10859,16 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -10902,7 +11094,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -10926,7 +11118,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="24" customHeight="1">
@@ -10973,16 +11165,16 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -11029,16 +11221,16 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -11264,7 +11456,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -11288,7 +11480,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="24" customHeight="1">
@@ -11335,16 +11527,16 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -11391,16 +11583,16 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -11626,7 +11818,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -11650,7 +11842,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="24" customHeight="1">
@@ -11697,19 +11889,19 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -11756,19 +11948,19 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="S3" s="5" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -12006,7 +12198,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -12030,7 +12222,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="24" customHeight="1">
@@ -12077,16 +12269,16 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -12133,16 +12325,16 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -12369,7 +12561,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -12393,7 +12585,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="24" customHeight="1">
@@ -12440,16 +12632,16 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -12496,16 +12688,16 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -12731,7 +12923,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -12755,7 +12947,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="24" customHeight="1">
@@ -12802,16 +12994,16 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -12858,16 +13050,16 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -13093,7 +13285,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -13117,7 +13309,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="24" customHeight="1">
@@ -13164,22 +13356,22 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -13226,22 +13418,22 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="S3" s="5" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="T3" s="5" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -13849,7 +14041,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -13873,7 +14065,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="24" customHeight="1">
@@ -13920,19 +14112,19 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="R2" s="3" t="s">
         <v>55</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -13979,19 +14171,19 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="R3" s="5" t="s">
         <v>55</v>
       </c>
       <c r="S3" s="5" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -14227,7 +14419,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -14251,7 +14443,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="24" customHeight="1">
@@ -14298,13 +14490,13 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="P2" s="3" t="s">
         <v>55</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="3" spans="1:17">
@@ -14351,13 +14543,13 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="P3" s="5" t="s">
         <v>55</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -14573,7 +14765,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -14597,7 +14789,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="24" customHeight="1">
@@ -14644,10 +14836,10 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -14694,10 +14886,10 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -14903,7 +15095,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -14927,7 +15119,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="24" customHeight="1">
@@ -14974,16 +15166,16 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="Q2" s="3" t="s">
         <v>55</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -15030,16 +15222,16 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="Q3" s="5" t="s">
         <v>55</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -15265,7 +15457,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -15289,7 +15481,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="24" customHeight="1">
@@ -15339,10 +15531,10 @@
         <v>24</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
     </row>
     <row r="3" spans="1:17">
@@ -15392,10 +15584,10 @@
         <v>24</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -15611,7 +15803,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -15635,7 +15827,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="24" customHeight="1">
@@ -15682,13 +15874,13 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="3" spans="1:17">
@@ -15735,13 +15927,13 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -15957,7 +16149,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -15981,7 +16173,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="24" customHeight="1">
@@ -16028,10 +16220,10 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -16078,10 +16270,10 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -16287,7 +16479,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -16311,7 +16503,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="24" customHeight="1">
@@ -16358,16 +16550,16 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -16414,16 +16606,16 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -16649,7 +16841,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -16673,7 +16865,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="24" customHeight="1">
@@ -16720,19 +16912,19 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="R2" s="3" t="s">
         <v>55</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -16779,19 +16971,19 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="R3" s="5" t="s">
         <v>55</v>
       </c>
       <c r="S3" s="5" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -17027,7 +17219,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -17051,7 +17243,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="24" customHeight="1">
@@ -17098,10 +17290,10 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -17148,10 +17340,10 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -17704,7 +17896,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -17728,7 +17920,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="24" customHeight="1">
@@ -17775,19 +17967,19 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="R2" s="3" t="s">
         <v>55</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -17834,19 +18026,19 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="R3" s="5" t="s">
         <v>55</v>
       </c>
       <c r="S3" s="5" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -18082,7 +18274,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -18106,7 +18298,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="24" customHeight="1">
@@ -18153,16 +18345,16 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -18209,16 +18401,16 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -18444,7 +18636,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -18468,7 +18660,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="24" customHeight="1">
@@ -18515,10 +18707,10 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -18565,10 +18757,10 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -18774,7 +18966,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -18798,7 +18990,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="24" customHeight="1">
@@ -18845,10 +19037,10 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="P2" s="3" t="s">
         <v>277</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -18895,10 +19087,10 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="P3" s="5" t="s">
         <v>277</v>
-      </c>
-      <c r="P3" s="5" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -19104,7 +19296,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -19128,7 +19320,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="24" customHeight="1">
@@ -19175,22 +19367,22 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -19237,22 +19429,22 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="S3" s="5" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="T3" s="5" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -19498,7 +19690,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -19522,7 +19714,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="24" customHeight="1">
@@ -19569,16 +19761,16 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="Q2" s="3" t="s">
         <v>55</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -19625,16 +19817,16 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="Q3" s="5" t="s">
         <v>55</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -19860,7 +20052,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -19884,7 +20076,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="24" customHeight="1">
@@ -19931,19 +20123,19 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -19990,19 +20182,19 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="S3" s="5" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -20238,7 +20430,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -20262,7 +20454,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="24" customHeight="1">
@@ -20309,19 +20501,19 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="R2" s="3" t="s">
         <v>55</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -20368,19 +20560,19 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="R3" s="5" t="s">
         <v>55</v>
       </c>
       <c r="S3" s="5" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -20616,7 +20808,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -20640,7 +20832,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="24" customHeight="1">
@@ -20687,16 +20879,16 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -20743,16 +20935,16 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -20979,7 +21171,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -21003,7 +21195,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="24" customHeight="1">
@@ -21056,7 +21248,7 @@
         <v>65</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3" spans="1:17">
@@ -21109,7 +21301,7 @@
         <v>65</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -21672,7 +21864,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -21696,7 +21888,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="24" customHeight="1">
@@ -21743,16 +21935,16 @@
         <v>22</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -21799,16 +21991,16 @@
         <v>22</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
     </row>
     <row r="4" spans="1:18">
